--- a/artfynd/A 63172-2023 artfynd.xlsx
+++ b/artfynd/A 63172-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63172-2023 artfynd.xlsx
+++ b/artfynd/A 63172-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61380983</v>
+        <v>76111334</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Herrhagsskogen, strax O om Källhagen, Upl</t>
+          <t>Stabby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>643915.3615547696</v>
+        <v>643903</v>
       </c>
       <c r="R2" t="n">
-        <v>6639163.560565873</v>
+        <v>6639069</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fynden gjordes mellan augusti och oktober 2018.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,20 +762,15 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Ca 35-årig gallrad granåker med +/- täckande skikt av markmossor</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Sofia Lundell, Karin Agstam-Norlin, Cecilia Rätz</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -926,6 +906,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>61380983</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Herrhagsskogen, strax O om Källhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>643915</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6639164</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-09-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ca 35-årig gallrad granåker med +/- täckande skikt av markmossor</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
